--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Banking & Financial Services Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Banking & Financial Services Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="132">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Banking &amp; Financial Services Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,21 +61,21 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
     <t>HDFC Bank Ltd.</t>
   </si>
   <si>
     <t>INE040A01034</t>
   </si>
   <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
     <t>Axis Bank Ltd.</t>
   </si>
   <si>
@@ -103,6 +103,12 @@
     <t>INE095A01012</t>
   </si>
   <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
     <t>Kotak Mahindra Bank Ltd.</t>
   </si>
   <si>
@@ -115,37 +121,58 @@
     <t>INE795G01014</t>
   </si>
   <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
     <t>Max Financial Services Ltd.</t>
   </si>
   <si>
     <t>INE180A01020</t>
   </si>
   <si>
-    <t>Bajaj Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE296A01024</t>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>Indian Energy Exchange Ltd.</t>
+  </si>
+  <si>
+    <t>INE022Q01020</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>City Union Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE491A01021</t>
+  </si>
+  <si>
+    <t>Muthoot Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE414G01012</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE414G01012</t>
+    <t>HDFC Asset Management Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE127D01025</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE115A01026</t>
+  </si>
+  <si>
+    <t>Anand Rathi Wealth Ltd.</t>
+  </si>
+  <si>
+    <t>INE463V01026</t>
   </si>
   <si>
     <t>SBI Cards &amp; Payment Services Ltd.</t>
@@ -154,51 +181,42 @@
     <t>INE018E01016</t>
   </si>
   <si>
-    <t>Indian Energy Exchange Ltd.</t>
-  </si>
-  <si>
-    <t>INE022Q01020</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Anand Rathi Wealth Ltd.</t>
-  </si>
-  <si>
-    <t>INE463V01026</t>
-  </si>
-  <si>
     <t>The Federal Bank Ltd.</t>
   </si>
   <si>
     <t>INE171A01029</t>
   </si>
   <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A01026</t>
-  </si>
-  <si>
     <t>Karur Vysya Bank Ltd.</t>
   </si>
   <si>
     <t>INE036D01028</t>
   </si>
   <si>
+    <t>Medi Assist Healthcare Services Ltd</t>
+  </si>
+  <si>
+    <t>INE456Z01021</t>
+  </si>
+  <si>
+    <t>CSB Bank Ltd</t>
+  </si>
+  <si>
+    <t>INE679A01013</t>
+  </si>
+  <si>
+    <t>Bajaj Finserv Ltd.</t>
+  </si>
+  <si>
+    <t>INE918I01026</t>
+  </si>
+  <si>
     <t>Go Digit General Insurance Ltd</t>
   </si>
   <si>
     <t>INE03JT01014</t>
   </si>
   <si>
-    <t>CSB Bank Ltd</t>
-  </si>
-  <si>
-    <t>INE679A01013</t>
-  </si>
-  <si>
     <t>Power Finance Corporation Ltd.</t>
   </si>
   <si>
@@ -211,16 +229,61 @@
     <t>INE063P01018</t>
   </si>
   <si>
-    <t>ICICI Prudential Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE726G01019</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda</t>
-  </si>
-  <si>
-    <t>INE028A01039</t>
+    <t>Rural Electrification Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE020B01018</t>
+  </si>
+  <si>
+    <t>RBL Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE976G01028</t>
+  </si>
+  <si>
+    <t>Bandhan Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE545U01014</t>
+  </si>
+  <si>
+    <t>CMS Info Systems Ltd</t>
+  </si>
+  <si>
+    <t>INE925R01014</t>
+  </si>
+  <si>
+    <t>Commercial Services &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Repco Home Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE612J01015</t>
+  </si>
+  <si>
+    <t>The Karnataka Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE614B01018</t>
+  </si>
+  <si>
+    <t>Fusion Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE139R01012</t>
+  </si>
+  <si>
+    <t>CreditAccess Grameen Ltd.</t>
+  </si>
+  <si>
+    <t>INE741K01010</t>
+  </si>
+  <si>
+    <t>Fusion Finance Ltd.- Partly Paid (Right Share)</t>
+  </si>
+  <si>
+    <t>IN9139R01028</t>
   </si>
   <si>
     <t>SBFC Finance Ltd</t>
@@ -229,82 +292,10 @@
     <t>INE423Y01016</t>
   </si>
   <si>
-    <t>360 One Wam Ltd.</t>
-  </si>
-  <si>
-    <t>INE466L01038</t>
-  </si>
-  <si>
-    <t>PNB Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE572E01012</t>
-  </si>
-  <si>
-    <t>Bandhan Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE545U01014</t>
-  </si>
-  <si>
-    <t>The Karnataka Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE614B01018</t>
-  </si>
-  <si>
-    <t>Fusion Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE139R01012</t>
-  </si>
-  <si>
-    <t>City Union Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE491A01021</t>
-  </si>
-  <si>
-    <t>CreditAccess Grameen Ltd.</t>
-  </si>
-  <si>
-    <t>INE741K01010</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE774D01024</t>
-  </si>
-  <si>
-    <t>CMS Info Systems Ltd</t>
-  </si>
-  <si>
-    <t>INE925R01014</t>
-  </si>
-  <si>
-    <t>Commercial Services &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Life Insurance Corporation of India</t>
-  </si>
-  <si>
-    <t>INE0J1Y01017</t>
-  </si>
-  <si>
-    <t>Zaggle Prepaid Ocean Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE07K301024</t>
-  </si>
-  <si>
-    <t>It - Services</t>
-  </si>
-  <si>
-    <t>Can Fin Homes Ltd.</t>
-  </si>
-  <si>
-    <t>INE477A01020</t>
+    <t>DCB Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE503A01015</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -343,25 +334,19 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X383</t>
+    <t>IN002025X034</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
-    <t>IN002024X417</t>
-  </si>
-  <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
     <t>364 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002023Z489</t>
-  </si>
-  <si>
-    <t>IN002024Z040</t>
+    <t>IN002024Z115</t>
+  </si>
+  <si>
+    <t>IN002025X042</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -394,13 +379,7 @@
     <t>ICICI Bank Ltd. $$</t>
   </si>
   <si>
-    <t>City Union Bank Ltd. $$</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd. $$</t>
-  </si>
-  <si>
-    <t>SBI Cards and Payment Services Ltd. $$</t>
+    <t>IndusInd Bank Ltd. $$</t>
   </si>
   <si>
     <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
@@ -418,7 +397,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -801,13 +780,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>120</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -825,7 +804,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="21412200"/>
+          <a:off x="666750" y="20459700"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -840,13 +819,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>120</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -864,7 +843,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="24269700"/>
+          <a:off x="666750" y="23317200"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1198,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J124"/>
+  <dimension ref="B1:J119"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1298,10 +1277,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>820523.92</v>
+        <v>882307.01</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9071008923357002</v>
+        <v>0.8991775832646002</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1335,10 +1314,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>820523.92</v>
+        <v>882307.01</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9071008923357002</v>
+        <v>0.8991775832646002</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1361,13 +1340,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>10891127</v>
+        <v>13361620</v>
       </c>
       <c r="G8" s="15">
-        <v>185013.02</v>
+        <v>193182.30</v>
       </c>
       <c r="H8" s="16">
-        <v>0.2045345314686</v>
+        <v>0.1968761345825</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1390,13 +1369,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>13445003</v>
+        <v>8660368</v>
       </c>
       <c r="G9" s="15">
-        <v>168439</v>
+        <v>168435.50</v>
       </c>
       <c r="H9" s="16">
-        <v>0.1862117160514</v>
+        <v>0.1716561515546</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1419,13 +1398,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>7015471</v>
+        <v>7188596</v>
       </c>
       <c r="G10" s="15">
-        <v>69179.56</v>
+        <v>85702.44</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0764789899208</v>
+        <v>0.0873411545027</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1448,13 +1427,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>6538064</v>
+        <v>9489675</v>
       </c>
       <c r="G11" s="15">
-        <v>50532.70</v>
+        <v>77084.63</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0558646203296</v>
+        <v>0.0785585635439</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1477,13 +1456,13 @@
         <v>26</v>
       </c>
       <c r="F12" s="14">
-        <v>3077155</v>
+        <v>2465619</v>
       </c>
       <c r="G12" s="15">
-        <v>45652.67</v>
+        <v>44681.95</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0504696775867</v>
+        <v>0.0455363126001</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1506,13 +1485,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>4371007</v>
+        <v>4229009</v>
       </c>
       <c r="G13" s="15">
-        <v>43325.42</v>
+        <v>34548.89</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0478968695305</v>
+        <v>0.0352094985788</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1532,16 +1511,16 @@
         <v>13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F14" s="14">
-        <v>1971184</v>
+        <v>1653762</v>
       </c>
       <c r="G14" s="15">
-        <v>37478.12</v>
+        <v>31014.65</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0414325960114</v>
+        <v>0.0316076804522</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1561,16 +1540,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F15" s="14">
-        <v>4439146</v>
+        <v>1448500</v>
       </c>
       <c r="G15" s="15">
-        <v>28323.97</v>
+        <v>30052.03</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0313125526694</v>
+        <v>0.030626654216</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1593,13 +1572,13 @@
         <v>26</v>
       </c>
       <c r="F16" s="14">
-        <v>1084898</v>
+        <v>3744946</v>
       </c>
       <c r="G16" s="15">
-        <v>20162.83</v>
+        <v>29092.61</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0222902960404</v>
+        <v>0.0296488891669</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1622,13 +1601,13 @@
         <v>26</v>
       </c>
       <c r="F17" s="14">
-        <v>1663281</v>
+        <v>1902703</v>
       </c>
       <c r="G17" s="15">
-        <v>18558.06</v>
+        <v>28591.92</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0205161999251</v>
+        <v>0.0291386254842</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1648,16 +1627,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F18" s="14">
-        <v>233740</v>
+        <v>3662288</v>
       </c>
       <c r="G18" s="15">
-        <v>18430.63</v>
+        <v>17492.92</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0203753242432</v>
+        <v>0.0178274017451</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1668,25 +1647,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="F19" s="14">
-        <v>3135025</v>
+        <v>5652542</v>
       </c>
       <c r="G19" s="15">
-        <v>13582.50</v>
+        <v>11336.17</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0150156474051</v>
+        <v>0.0115529286615</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1706,16 +1685,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F20" s="14">
-        <v>584889</v>
+        <v>5594213</v>
       </c>
       <c r="G20" s="15">
-        <v>13211.47</v>
+        <v>10947.87</v>
       </c>
       <c r="H20" s="16">
-        <v>0.01460546845</v>
+        <v>0.0111572039856</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1735,16 +1714,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F21" s="14">
-        <v>1511822</v>
+        <v>490645</v>
       </c>
       <c r="G21" s="15">
-        <v>11765</v>
+        <v>10869.75</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0130063752417</v>
+        <v>0.0110775902547</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1755,25 +1734,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F22" s="14">
-        <v>5652542</v>
+        <v>177465</v>
       </c>
       <c r="G22" s="15">
-        <v>9869.34</v>
+        <v>8488.15</v>
       </c>
       <c r="H22" s="16">
-        <v>0.010910696084</v>
+        <v>0.0086504517326</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1793,16 +1772,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F23" s="14">
-        <v>225120</v>
+        <v>1422276</v>
       </c>
       <c r="G23" s="15">
-        <v>8244.34</v>
+        <v>8483.17</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0091142354152</v>
+        <v>0.0086453765102</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1822,16 +1801,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F24" s="14">
-        <v>3546028</v>
+        <v>450240</v>
       </c>
       <c r="G24" s="15">
-        <v>6638.52</v>
+        <v>8448.75</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0073389785099</v>
+        <v>0.0086102983661</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1851,16 +1830,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F25" s="14">
-        <v>1077352</v>
+        <v>891004</v>
       </c>
       <c r="G25" s="15">
-        <v>6443.64</v>
+        <v>8206.59</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0071235358914</v>
+        <v>0.0083635080299</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1883,13 +1862,13 @@
         <v>17</v>
       </c>
       <c r="F26" s="14">
-        <v>2653170</v>
+        <v>3546028</v>
       </c>
       <c r="G26" s="15">
-        <v>6320.38</v>
+        <v>7165.10</v>
       </c>
       <c r="H26" s="16">
-        <v>0.006987270204</v>
+        <v>0.0073021037222</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1909,16 +1888,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F27" s="14">
-        <v>2027126</v>
+        <v>3169081</v>
       </c>
       <c r="G27" s="15">
-        <v>6034.75</v>
+        <v>7025.54</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0066715021666</v>
+        <v>0.0071598751984</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1938,16 +1917,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F28" s="14">
-        <v>1803900</v>
+        <v>1387119</v>
       </c>
       <c r="G28" s="15">
-        <v>5521.74</v>
+        <v>6871.09</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0061043622972</v>
+        <v>0.0070024719633</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1967,16 +1946,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F29" s="14">
-        <v>1233282</v>
+        <v>1800763</v>
       </c>
       <c r="G29" s="15">
-        <v>5210.62</v>
+        <v>6570.08</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0057604147014</v>
+        <v>0.0066957063576</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1996,16 +1975,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F30" s="14">
-        <v>7724547</v>
+        <v>275535</v>
       </c>
       <c r="G30" s="15">
-        <v>5136.82</v>
+        <v>5558.64</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0056788277491</v>
+        <v>0.0056649266352</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2028,13 +2007,13 @@
         <v>26</v>
       </c>
       <c r="F31" s="14">
-        <v>744667</v>
+        <v>1586343</v>
       </c>
       <c r="G31" s="15">
-        <v>4587.15</v>
+        <v>5472.88</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0050711597271</v>
+        <v>0.0055775268201</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2054,16 +2033,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F32" s="14">
-        <v>2094737</v>
+        <v>1233282</v>
       </c>
       <c r="G32" s="15">
-        <v>4469.96</v>
+        <v>5006.51</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0049416045113</v>
+        <v>0.0051022393694</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2083,16 +2062,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F33" s="14">
-        <v>5107337</v>
+        <v>7724547</v>
       </c>
       <c r="G33" s="15">
-        <v>4354</v>
+        <v>4913.58</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0048134090779</v>
+        <v>0.0050075324569</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2112,16 +2091,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F34" s="14">
-        <v>383211</v>
+        <v>1127230</v>
       </c>
       <c r="G34" s="15">
-        <v>3861.81</v>
+        <v>4534.85</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0042692860154</v>
+        <v>0.0046215607688</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2141,16 +2120,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F35" s="14">
-        <v>392278</v>
+        <v>1850686</v>
       </c>
       <c r="G35" s="15">
-        <v>3444.99</v>
+        <v>3943.26</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0038084855626</v>
+        <v>0.0040186589892</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2173,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="F36" s="14">
-        <v>1731635</v>
+        <v>2271620</v>
       </c>
       <c r="G36" s="15">
-        <v>2621.35</v>
+        <v>3866.07</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0028979397994</v>
+        <v>0.0039399930409</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2199,16 +2178,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="F37" s="14">
-        <v>1276505</v>
+        <v>655656</v>
       </c>
       <c r="G37" s="15">
-        <v>2446.8</v>
+        <v>3226.16</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0027049722857</v>
+        <v>0.0032878473356</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2219,25 +2198,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F38" s="14">
-        <v>1354539</v>
+        <v>746965</v>
       </c>
       <c r="G38" s="15">
-        <v>2395.91</v>
+        <v>2916.52</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0026487126651</v>
+        <v>0.0029722867158</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2248,10 +2227,10 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>13</v>
@@ -2260,13 +2239,13 @@
         <v>17</v>
       </c>
       <c r="F39" s="14">
-        <v>1225000</v>
+        <v>1276505</v>
       </c>
       <c r="G39" s="15">
-        <v>2128.07</v>
+        <v>2526.33</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0023526117263</v>
+        <v>0.0025746359013</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2277,25 +2256,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F40" s="14">
-        <v>161776</v>
+        <v>1354539</v>
       </c>
       <c r="G40" s="15">
-        <v>1751.79</v>
+        <v>2303.94</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0019366288214</v>
+        <v>0.0023479935869</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2306,25 +2285,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F41" s="14">
-        <v>561937</v>
+        <v>161776</v>
       </c>
       <c r="G41" s="15">
-        <v>1601.24</v>
+        <v>1851.53</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0017701936499</v>
+        <v>0.0018869330651</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2335,25 +2314,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="F42" s="14">
-        <v>341331</v>
+        <v>1092590</v>
       </c>
       <c r="G42" s="15">
-        <v>1479.16</v>
+        <v>1152.35</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0016352324694</v>
+        <v>0.0011743840594</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2373,16 +2352,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F43" s="14">
-        <v>132738</v>
+        <v>460782</v>
       </c>
       <c r="G43" s="15">
-        <v>1122.23</v>
+        <v>520.32</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0012406412654</v>
+        <v>0.0005302690274</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2402,16 +2381,16 @@
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="F44" s="14">
-        <v>172436</v>
+        <v>151000</v>
       </c>
       <c r="G44" s="15">
-        <v>762.17</v>
+        <v>221.97</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0008425898017</v>
+        <v>0.0002262142835</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2422,435 +2401,435 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="15" customHeight="1">
+      <c r="B46" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="H46" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F45" s="14">
-        <v>63230</v>
-      </c>
-      <c r="G45" s="15">
-        <v>422.19</v>
-      </c>
-      <c r="H45" s="16">
-        <v>0.0004667370644</v>
-      </c>
-      <c r="I45" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="7" t="s">
+      <c r="C48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="15" customHeight="1">
+      <c r="B49" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15" customHeight="1">
+      <c r="B51" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" customHeight="1">
+      <c r="B52" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="C52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="H47" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="7" t="s">
+      <c r="C54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="15" customHeight="1">
+      <c r="B55" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="7" t="s">
+      <c r="C56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="15" customHeight="1">
+      <c r="B58" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="7" t="s">
+      <c r="C58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1">
+      <c r="B59" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1">
+      <c r="B60" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="7" t="s">
+      <c r="C60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="9">
+        <v>12934.72</v>
+      </c>
+      <c r="H60" s="10">
+        <v>0.0131820445014</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1">
+      <c r="B61" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="15" customHeight="1">
+      <c r="B62" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" ht="15" customHeight="1">
-      <c r="B58" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="7" t="s">
+      <c r="C62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1">
+      <c r="B63" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1">
+      <c r="B64" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" ht="15" customHeight="1">
-      <c r="B60" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="15" customHeight="1">
-      <c r="B61" s="7" t="s">
+      <c r="C64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1">
+      <c r="B65" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15" customHeight="1">
+      <c r="B66" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="9">
-        <v>18302.31</v>
-      </c>
-      <c r="H61" s="10">
-        <v>0.020233464653399997</v>
-      </c>
-      <c r="I61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" ht="15" customHeight="1">
-      <c r="B62" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="15" customHeight="1">
-      <c r="B63" s="7" t="s">
+      <c r="C66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="9">
+        <v>12934.72</v>
+      </c>
+      <c r="H66" s="10">
+        <v>0.0131820445014</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15" customHeight="1">
+      <c r="B67" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="15" customHeight="1">
-      <c r="B64" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="7" t="s">
+      <c r="C67" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="7" t="s">
+      <c r="D67" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C67" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="9">
-        <v>18302.31</v>
-      </c>
-      <c r="H67" s="10">
-        <v>0.020233464653399997</v>
-      </c>
-      <c r="I67" s="9" t="s">
-        <v>13</v>
+      <c r="F67" s="14">
+        <v>7500000</v>
+      </c>
+      <c r="G67" s="15">
+        <v>7447.33</v>
+      </c>
+      <c r="H67" s="16">
+        <v>0.0075897302359</v>
+      </c>
+      <c r="I67" s="15">
+        <v>5.61</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>13</v>
@@ -2867,19 +2846,19 @@
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F68" s="14">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="G68" s="15">
-        <v>9904.11</v>
+        <v>4991.43</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0109491348147</v>
+        <v>0.0050868710251</v>
       </c>
       <c r="I68" s="15">
-        <v>6.43</v>
+        <v>5.70</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>13</v>
@@ -2887,28 +2866,28 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F69" s="14">
-        <v>6000000</v>
+        <v>500000</v>
       </c>
       <c r="G69" s="15">
-        <v>5920.71</v>
+        <v>495.96</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0065454293206</v>
+        <v>0.0005054432404</v>
       </c>
       <c r="I69" s="15">
-        <v>6.52</v>
+        <v>5.61</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>13</v>
@@ -2916,57 +2895,36 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F70" s="14">
-        <v>1300000</v>
-      </c>
-      <c r="G70" s="15">
-        <v>1281.25</v>
-      </c>
-      <c r="H70" s="16">
-        <v>0.0014164401426</v>
-      </c>
-      <c r="I70" s="15">
-        <v>6.51</v>
+        <v>13</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
-      <c r="B71" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F71" s="14">
-        <v>1100000</v>
-      </c>
-      <c r="G71" s="15">
-        <v>1097.68</v>
-      </c>
-      <c r="H71" s="16">
-        <v>0.0012135008903</v>
-      </c>
-      <c r="I71" s="15">
-        <v>6.42</v>
+      <c r="B71" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
@@ -2974,138 +2932,131 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15" customHeight="1">
+      <c r="B73" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1">
+      <c r="B74" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1">
+      <c r="B75" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="9">
+        <v>90211.34</v>
+      </c>
+      <c r="H75" s="10">
+        <v>0.0919362690821</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1">
+      <c r="B76" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1">
+      <c r="B77" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="9">
+        <v>2224.11924</v>
+      </c>
+      <c r="H77" s="10">
+        <v>0.0022666465759</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15" customHeight="1">
+      <c r="B78" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D72" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F72" s="14">
-        <v>100000</v>
-      </c>
-      <c r="G72" s="15">
-        <v>98.56</v>
-      </c>
-      <c r="H72" s="16">
-        <v>0.0001089594852</v>
-      </c>
-      <c r="I72" s="15">
-        <v>6.51</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" ht="15" customHeight="1">
-      <c r="B75" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="9">
-        <v>66165</v>
-      </c>
-      <c r="H78" s="10">
-        <v>0.0731463508602</v>
-      </c>
-      <c r="I78" s="9" t="s">
+      <c r="C78" s="13"/>
+      <c r="D78" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="13"/>
+      <c r="G78" s="15">
+        <v>2224.11924</v>
+      </c>
+      <c r="H78" s="16">
+        <v>0.0022666465759</v>
+      </c>
+      <c r="I78" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J78" s="11" t="s">
@@ -3121,302 +3072,213 @@
       </c>
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="18">
+        <v>-6439.41550154984</v>
+      </c>
+      <c r="H80" s="19">
+        <v>-0.006562543426162753</v>
+      </c>
+      <c r="I80" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1">
+      <c r="B81" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="18">
+        <v>981237.77373845</v>
+      </c>
+      <c r="H81" s="19">
+        <v>0.9999999999978372</v>
+      </c>
+      <c r="I81" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" ht="15" customHeight="1">
+      <c r="B83" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H83" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" ht="15" customHeight="1">
+      <c r="B84" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G84" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H84" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" ht="15" customHeight="1">
+      <c r="B85" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="9">
-        <v>1994.11924</v>
-      </c>
-      <c r="H80" s="10">
-        <v>0.0022045272513</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="12" t="s">
+      <c r="C85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1">
+      <c r="B86" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C81" s="13"/>
-      <c r="D81" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="13"/>
-      <c r="G81" s="15">
-        <v>1994.11924</v>
-      </c>
-      <c r="H81" s="16">
-        <v>0.0022045272513</v>
-      </c>
-      <c r="I81" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="17" t="s">
+      <c r="C86" s="13"/>
+      <c r="D86" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" s="14">
+        <v>726600</v>
+      </c>
+      <c r="G86" s="15">
+        <v>10574.21</v>
+      </c>
+      <c r="H86" s="16">
+        <v>0.0107763992408</v>
+      </c>
+      <c r="I86" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1">
+      <c r="B87" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C83" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="18">
-        <v>-2428.9466047799215</v>
-      </c>
-      <c r="H83" s="19">
-        <v>-0.002685235102757259</v>
-      </c>
-      <c r="I83" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="17" t="s">
+      <c r="C87" s="13"/>
+      <c r="D87" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="14">
+        <v>-2185000</v>
+      </c>
+      <c r="G87" s="15">
+        <v>-17917</v>
+      </c>
+      <c r="H87" s="16">
+        <v>-0.0182595905697</v>
+      </c>
+      <c r="I87" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" ht="15" customHeight="1">
+      <c r="B91" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C84" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G84" s="18">
-        <v>904556.40263522</v>
-      </c>
-      <c r="H84" s="19">
-        <v>0.9999999999978426</v>
-      </c>
-      <c r="I84" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="18" t="s">
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="21"/>
+      <c r="G91" s="21"/>
+      <c r="H91" s="21"/>
+      <c r="I91" s="21"/>
+    </row>
+    <row r="95" spans="2:9" ht="15" customHeight="1">
+      <c r="B95" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H86" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C87" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D87" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E87" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G87" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="H87" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="7" t="s">
+      <c r="C95" s="21"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="21"/>
+      <c r="G95" s="21"/>
+      <c r="H95" s="21"/>
+      <c r="I95" s="21"/>
+    </row>
+    <row r="96" spans="2:8" ht="15" customHeight="1">
+      <c r="B96" s="13" t="s">
         <v>124</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H88" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F89" s="14">
-        <v>995400</v>
-      </c>
-      <c r="G89" s="15">
-        <v>12516.66</v>
-      </c>
-      <c r="H89" s="16">
-        <v>0.0138373460886</v>
-      </c>
-      <c r="I89" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F90" s="14">
-        <v>1150000</v>
-      </c>
-      <c r="G90" s="15">
-        <v>2004.91</v>
-      </c>
-      <c r="H90" s="16">
-        <v>0.0022164565903</v>
-      </c>
-      <c r="I90" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J90" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C91" s="13"/>
-      <c r="D91" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F91" s="14">
-        <v>173125</v>
-      </c>
-      <c r="G91" s="15">
-        <v>1714.72</v>
-      </c>
-      <c r="H91" s="16">
-        <v>0.0018956474079</v>
-      </c>
-      <c r="I91" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C92" s="13"/>
-      <c r="D92" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F92" s="14">
-        <v>68800</v>
-      </c>
-      <c r="G92" s="15">
-        <v>536.40</v>
-      </c>
-      <c r="H92" s="16">
-        <v>0.0005929978478</v>
-      </c>
-      <c r="I92" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9" ht="15" customHeight="1">
-      <c r="B96" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="C96" s="21"/>
       <c r="D96" s="21"/>
@@ -3424,11 +3286,43 @@
       <c r="F96" s="21"/>
       <c r="G96" s="21"/>
       <c r="H96" s="21"/>
-      <c r="I96" s="21"/>
-    </row>
-    <row r="100" spans="2:9" ht="15" customHeight="1">
-      <c r="B100" s="13" t="s">
-        <v>130</v>
+    </row>
+    <row r="97" spans="2:8" ht="15" customHeight="1">
+      <c r="B97" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="21"/>
+      <c r="G97" s="21"/>
+      <c r="H97" s="21"/>
+    </row>
+    <row r="98" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B98" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C98" s="21"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="21"/>
+      <c r="F98" s="21"/>
+      <c r="G98" s="21"/>
+      <c r="H98" s="21"/>
+    </row>
+    <row r="99" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B99" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="21"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+    </row>
+    <row r="100" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B100" s="22" t="s">
+        <v>128</v>
       </c>
       <c r="C100" s="21"/>
       <c r="D100" s="21"/>
@@ -3436,90 +3330,34 @@
       <c r="F100" s="21"/>
       <c r="G100" s="21"/>
       <c r="H100" s="21"/>
-      <c r="I100" s="21"/>
-    </row>
-    <row r="101" spans="2:8" ht="15" customHeight="1">
-      <c r="B101" s="13" t="s">
+    </row>
+    <row r="103" ht="15">
+      <c r="B103" s="21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="118" ht="15">
+      <c r="B118" s="21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="119" ht="15">
+      <c r="B119" s="21" t="s">
         <v>131</v>
-      </c>
-      <c r="C101" s="21"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21"/>
-      <c r="G101" s="21"/>
-      <c r="H101" s="21"/>
-    </row>
-    <row r="102" spans="2:8" ht="15" customHeight="1">
-      <c r="B102" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C102" s="21"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21"/>
-      <c r="G102" s="21"/>
-      <c r="H102" s="21"/>
-    </row>
-    <row r="103" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B103" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="C103" s="21"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21"/>
-      <c r="G103" s="21"/>
-      <c r="H103" s="21"/>
-    </row>
-    <row r="104" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B104" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C104" s="21"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="21"/>
-      <c r="F104" s="21"/>
-      <c r="G104" s="21"/>
-      <c r="H104" s="21"/>
-    </row>
-    <row r="105" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B105" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="C105" s="21"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="21"/>
-      <c r="G105" s="21"/>
-      <c r="H105" s="21"/>
-    </row>
-    <row r="108" ht="15">
-      <c r="B108" s="21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="123" ht="15">
-      <c r="B123" s="21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="124" ht="15">
-      <c r="B124" s="21" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B101:H101"/>
-    <mergeCell ref="B102:H102"/>
-    <mergeCell ref="B103:H103"/>
-    <mergeCell ref="B104:H104"/>
-    <mergeCell ref="B105:H105"/>
+    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B98:H98"/>
+    <mergeCell ref="B99:H99"/>
+    <mergeCell ref="B100:H100"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B96:I96"/>
-    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="B91:I91"/>
+    <mergeCell ref="B95:I95"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
